--- a/docs/perechen-otchetov/obrazcy/ФО-11.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-11.xlsx
@@ -7,18 +7,27 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Образец" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ФО-11" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вид 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вид 1 — параметры" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'ФО-11'!$5:$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Вид 1'!$5:$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+  </numFmts>
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,14 +36,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="9"/>
     </font>
     <font>
@@ -50,12 +91,27 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0044546A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009BC2E6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -89,56 +145,100 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -504,286 +604,314 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="7.8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Информация по списанию</t>
+          <t>ОАО «Государственный финансовый холдинг»</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>ФО-11</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>за период с 01.09.2026 по 30.09.2026, сом</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Кол-во субъектов</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Кол-во списаний</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Списание задолженности</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>за период с 01.09.2026 по 30.09.2026, тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Списание</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Дата списания</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Основание</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Всего</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Основная сумма</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Проценты</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Штрафы</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Вид списания</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Заёмщиков</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Кредитов</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Списаний</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Всего списано</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>в том числе</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>по основной сумме</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>по процентам</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>по штрафам</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="6" t="n">
-        <v>900500</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>750000</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>112500</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>38000</v>
-      </c>
-      <c r="J6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="E8" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="F8" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>г. Бишкек</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="6" t="n">
-        <v>900500</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>750000</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>112500</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>38000</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="G8" s="9" t="n">
+        <v>900.5</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Департамент администрирования кредитов</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="E9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>г. Бишкек</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="10" t="n">
-        <v>900500</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>112500</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>38000</v>
-      </c>
-      <c r="J8" s="9" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr"/>
-      <c r="B9" s="7" t="n">
+      <c r="F9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="G9" s="13" t="n">
+        <v>900.5</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>750</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>ОсОО «Тянь-Шань Металл»</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="10" t="n">
-        <v>900500</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>112500</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>38000</v>
-      </c>
-      <c r="J9" s="9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr"/>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>№ 20-3/052 от 21.07.2020</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="10" t="n">
-        <v>900500</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>112500</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>38000</v>
-      </c>
-      <c r="J10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr"/>
-      <c r="B11" s="9" t="inlineStr"/>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>списание</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>17.09.2026</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="F10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>900.5</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>750</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>№ 20-3/052 от 21.07.2020, KGS</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>900.5</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>750</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Заключение Постоянно-действующей комиссии № 31 от 10.09.2026</t>
         </is>
       </c>
-      <c r="F11" s="10" t="n">
-        <v>900500</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>112500</v>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>38000</v>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>Признана безнадёжной; списан весь долг</t>
-        </is>
+      <c r="B12" s="22" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>весь долг</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="25" t="n">
+        <v>900.5</v>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>750</v>
+      </c>
+      <c r="I12" s="25" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="J12" s="25" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
+  <mergeCells count="10">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.39" right="0.39" top="0.39" bottom="0.39" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Arial"&amp;8 ФО-11 · сформировал Бекова Н. С. 06.10.2026 11:30 · Страница &amp;P из &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -793,7 +921,627 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Параметры отчёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>ФО-11 «Списание задолженности за период»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Период</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>01.09.2026 – 30.09.2026 (по умолчанию — прошлый месяц)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Отбор</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Единица</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Департамент → Заёмщик → Кредит → списание</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>Реквизиты разрезов</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>на дату списания</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>Курсы валют</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>списание по валютному кредиту — по курсу на день списания; таких списаний за период нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>Период закрыт</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>сентябрь 2026 — закрыт 05.10.2026; исправлений после закрытия нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Рассчитан</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>06.10.2026 09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Сформировал</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Бекова Н. С.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Округление</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>В ячейках — точные суммы, на экране и в печати — тыс. сом с двумя знаками. Итоги считаются по точным суммам, поэтому сумма округлённых строк может отличаться от итога на 0,01.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="7.8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ОАО «Государственный финансовый холдинг»</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>ФО-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Списанная задолженность</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>по состоянию на 01.10.2026, тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Дата списания</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Заёмщиков</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Кредитов</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Всего списано</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>в том числе</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Поступило после списания</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Не возвращено</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>по основной сумме</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>по процентам</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>по штрафам</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>900.5</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>900.5</v>
+      </c>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Департамент администрирования кредитов</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>900.5</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>750</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>900.5</v>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>ОсОО «Тянь-Шань Металл»</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>900.5</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>750</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>900.5</v>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>№ 20-3/052 от 21.07.2020, KGS</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>не ведётся</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="25" t="n">
+        <v>900.5</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>750</v>
+      </c>
+      <c r="H11" s="25" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="I11" s="25" t="n">
+        <v>38</v>
+      </c>
+      <c r="J11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="25" t="n">
+        <v>900.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+  </mergeCells>
+  <pageMargins left="0.39" right="0.39" top="0.39" bottom="0.39" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Arial"&amp;8 ФО-11 · сформировал Бекова Н. С. 06.10.2026 11:35 · Страница &amp;P из &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Параметры отчёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>ФО-11 «Списанная задолженность по состоянию на дату» — вид отчёта «Списание задолженности за период»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Дата состояния</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>01.10.2026 (данные на конец 30.09.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Отбор</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Единица</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Департамент → Заёмщик → кредит</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>Курсы валют</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>списано — по курсу на день списания; не возвращено — на 30.09.2026: USD 87,50000, EUR 101,50000; списанных кредитов в валюте нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>Период</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>сентябрь 2026 — закрыт 05.10.2026; исправлений после закрытия нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>Рассчитан</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>06.10.2026 09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Сформировал</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Бекова Н. С.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Округление</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>В ячейках — точные суммы, на экране и в печати — тыс. сом с двумя знаками. Итоги считаются по точным суммам, поэтому сумма округлённых строк может отличаться от итога на 0,01.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -802,440 +1550,629 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>ФО-11 «Списание задолженности» — карточка</t>
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>ФО-11 «Списание задолженности за период» — карточка</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>ФО-11</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Списание задолженности</t>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>Списание задолженности за период</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Часть</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Модуль</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>Кредит</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Получатель</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Язык</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶417; Порядок №41 пп. 62–63; Политика №28 п. 4.1.1 пп. 9, 12; старая система</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Образец-основа</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>старая система «Отчет по списанию»</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+    <row r="11" ht="135" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Кому и зачем</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>Правлению и департаментам — какая задолженность списана за период, на каком основании и в каких суммах.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>Руководству Холдинга, Департаменту администрирования кредитов и Департаменту регионального развития, бухгалтерии — какая задолженность списана за период: по каким кредитам, на каком основании и сколько по основной сумме, процентам и штрафам. Бухгалтерия сверяет отчёт после закрытия месяца: списано по процентам и штрафам = ФО-07, остаток списанного кредита в ФО-02 — 0,00. Списание — не платёж и в погашения (ФО-04) не входит. Сколько списанной задолженности ещё взыскивается и сколько вернулось после списания — вид «Списанная задолженность по состоянию на дату». Признание задолженности безнадёжной без решения о списании — не списание: такие кредиты видны в ФО-02 по группе платёжеспособности. В старой системе — «Отчет по списанию» («Информация по списанию»), по состоянию на дату.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Когда</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>За период (по умолчанию — прошлый месяц); по требованию.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="75" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>За период: ежемесячно после закрытия месяца и по требованию; по умолчанию — прошлый месяц. Можно выбрать любой период (за год — с 1 января).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Параметры</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>• Период — прошлый месяц
-• Подразделение — все
-• Единица — сом
-• Разрезы — по умолчанию Область → Район → Заёмщик → Кредит → Списание</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>• Период — прошлый месяц; можно выбрать любой
+• Единица — тыс. сом (можно выбрать «сом»)
+• Разрезы — до шести уровней в любом порядке; по умолчанию департамент → заёмщик → кредит → списание. Доступны: департамент, отдел, куратор, область, район, отрасль, кредитная программа, вид кредита, кредитная линия, валюта, вид списания, месяц, заёмщик, кредит
+• Отбор — по любому из разрезов</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="300" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Строки</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Область → район → заёмщик → кредит → списание. Подытоги на каждом уровне, сверху ИТОГО. Списания — по дате. Дата, основание и примечание выводятся в строке списания; в строке кредита — итоги по нему.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>Строка детали — списание: запись о списании задолженности по решению; в «Наименовании» — документ-основание «&lt;вид документа&gt; № … от …», в колонках — дата списания, вид списания и суммы по статьям. В отчёт попадают записи о списании с датой списания в периоде. Не списание и в отчёт не входят: признание задолженности безнадёжной без решения о списании, закрытие копеечного остатка при погашении, перевод долга (ФО-12), принятие имущества в счёт погашения (ФО-04). Суммы — по трём статьям, как в ФО-02 и ФО-04: основная сумма; проценты — вместе с накопленными и платой за неосвоенный остаток; штрафы — пеня по основной сумме и по процентам вместе с накопленной. Списанные сборы и расходы по взысканию в отчёт не входят. Показывается снятое с кредита — числившееся на день списания: если в документе названа бо́льшая сумма, в отчёте её нет. «Всего списано» = основная сумма + проценты + штрафы. Вид списания — «весь долг», если после списания долг по кредиту (основная сумма, проценты, штрафы) — 0,00 и кредит закрыт, иначе «часть долга». Над списаниями разрезы, по умолчанию департамент → заёмщик → кредит; строка кредита «№ … от …, KGS» есть всегда, даже при одном списании; при разрезе по области у городов республиканского значения — обе строки, области и района. Реквизиты разрезов (департамент, отдел, куратор) — на дату списания. Первая строка — ИТОГО; строка разреза несёт его итог и стоит над своими строками. Порядок: департаменты и отделы — по оргструктуре; заёмщики — по алфавиту наименования без организационной формы; кредиты заёмщика — по дате договора; списания кредита — по дате списания. Суммы — в тыс. сом. Кредит в иностранной валюте: суммы в сомах по курсу на день списания, под строкой списания курсивом строка «в тыс. &lt;валюта&gt; (курс …)» с теми же суммами в валюте договора; в итоги она не входит. Печать — A4 альбомная.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>по умолчанию: Департамент → Заёмщик → Кредит → списание; можно выбрать: Департамент, Отдел, Куратор, Область, Район, Отрасль, Кредитная программа, Вид кредита, Кредитная линия, Валюта, Вид списания, Месяц, Заёмщик, Кредит</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>Если строк нет</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>Списаний задолженности за период по условиям отбора нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>Выгрузка</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>xlsx, pdf</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>Прежнее название в старой системе — «Отчет по списанию» («Информация по списанию», по состоянию на дату)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t>Колонки</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Колонка</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>Общая шапка</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>Что в ней</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Кол-во субъектов</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr"/>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>число заёмщиков со списанием в группе</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Кол-во списаний</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr"/>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>число списаний в группе</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr"/>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>область, район, заёмщик или номер договора</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr"/>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>департамент, заёмщик, кредит «№ … от …, KGS» или списание — документ-основание «&lt;вид документа&gt; № … от …» — по уровню строки</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>Дата списания</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>Списание</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>дата списания; у строки списания</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr"/>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>дата, с которой задолженность снята с кредита (дата записи о списании); заполняется у списания</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>Вид списания</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr"/>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>«весь долг» — после списания долг по кредиту 0,00, кредит закрыт; «часть долга» — долг остался; заполняется у списания</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>Заёмщиков</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr"/>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>число заёмщиков со списанием в разрезе; у заёмщика и ниже пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>Кредитов</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr"/>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>число кредитов со списанием; у кредита и списания пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>Списаний</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="inlineStr"/>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>число записей о списании; у списания пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>Всего списано</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr"/>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>основная сумма + проценты + штрафы</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>по основной сумме</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>в том числе</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>списано основной суммы</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>по процентам</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>в том числе</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>списано процентов вместе с накопленными и платой за неосвоенный остаток; = ФО-07 «списано» по процентам</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>по штрафам</t>
+        </is>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>в том числе</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>списано пени по основной сумме и по процентам вместе с накопленной; = ФО-07 «списано» по штрафам</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>Правила проверки</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026: 1 заёмщик, 1 кредит, 1 списание — КЗ-08 ОсОО «Тянь-Шань Металл», № 20-3/052 от 21.07.2020, списан 17.09.2026 по заключению Постоянно-действующей комиссии № 31 от 10.09.2026: всего 900,500 тыс. сом = основная сумма 750,000 + проценты 112,500 + штрафы 38,000; вид списания — «весь долг».</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B35" s="32" t="inlineStr">
+        <is>
+          <t>«Всего списано» каждой строки = по основной сумме + по процентам + по штрафам; строка разреза = сумма строк на уровень ниже по каждой сумме и счётчику.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B36" s="32" t="inlineStr">
+        <is>
+          <t>Списано по процентам и штрафам = ФО-07 за тот же период: 112,500 и 38,000. Проценты и штрафы — числившиеся на день списания: проценты 109,167 на начало сентября + начислено по 17.09.2026 3,333; штрафы 36,800 + 1,200.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B37" s="32" t="inlineStr">
+        <is>
+          <t>В ФО-02 на 01.10.2026 остаток КЗ-08 — 0,00; в ФО-04 за сентябрь списание не показано; в ФО-58 — то же событие «Закрытие: списан» 17.09.2026 с тем же основанием.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="31" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B38" s="32" t="inlineStr">
+        <is>
+          <t>Не попадают: КЗ-15 (погашен 18.09.2026 — ФО-95), КЗ-07 (перевод долга 09.09.2026 — ФО-12), КЗ-16 (погашен имуществом 20.03.2026 — ФО-04), кредиты в группе «4. Безнадёжные долги» без решения о списании.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B39" s="32" t="inlineStr">
+        <is>
+          <t>Период 01.01.2026–30.09.2026 — то же одно списание: других списаний в контрольном наборе нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t>Вид 1: «Списанная задолженность по состоянию на дату» — лист «Вид 1»</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="120" customHeight="1">
+      <c r="A42" s="31" t="inlineStr">
+        <is>
+          <t>Кому и зачем</t>
+        </is>
+      </c>
+      <c r="B42" s="32" t="inlineStr">
+        <is>
+          <t>Руководству Холдинга, Департаменту администрирования кредитов и Департаменту регионального развития, бухгалтерии — внебалансовый учёт списанной задолженности: по каждому кредиту со списанием — сколько списано за всё время, сколько поступило после списания, сколько не возвращено и идёт ли ещё взыскание. Списание — учётное действие: оно не отзывает исполнительный лист, не прекращает производство и не снимает обременение; деньги, поступившие после списания, разносятся обычным порядком и помечаются как погашение списанной задолженности. Какие списания были за период и на каком основании — основной отчёт ФО-11. Новая форма: в старой системе поступлений после списания не было ни в одном отчёте.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>Когда</t>
+        </is>
+      </c>
+      <c r="B43" s="32" t="inlineStr">
+        <is>
+          <t>По состоянию на дату, по требованию; по умолчанию — сегодня (данные на конец предыдущего дня). Можно выбрать любую дату.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="120" customHeight="1">
+      <c r="A44" s="31" t="inlineStr">
+        <is>
+          <t>Параметры</t>
+        </is>
+      </c>
+      <c r="B44" s="32" t="inlineStr">
+        <is>
+          <t>• Дата — сегодня (данные на конец предыдущего дня); можно выбрать любую
+• Единица — тыс. сом (можно выбрать «сом»)
+• Разрезы — до шести уровней в любом порядке; по умолчанию департамент → заёмщик → кредит. Доступны: департамент, отдел, куратор, взыскание, область, район, отрасль, кредитная программа, вид кредита, кредитная линия, валюта, год списания, заёмщик
+• Отбор — по любому из разрезов; только кредиты с поступлениями после списания</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="240" customHeight="1">
+      <c r="A45" s="31" t="inlineStr">
+        <is>
+          <t>Строки</t>
+        </is>
+      </c>
+      <c r="B45" s="32" t="inlineStr">
+        <is>
+          <t>Строка детали — кредит, по которому по дату отчёта включительно было хотя бы одно списание. Списано — сумма всех списаний кредита по дату отчёта, по тем же трём статьям, что в основном отчёте; дата списания — последнего. Поступило после списания — деньги, поступившие по кредиту после дня списания и помеченные как погашение списанной задолженности, в сомах, как поступили. Не возвращено = списано − поступило после списания. Взыскание — «идёт», если на дату отчёта по кредиту есть иск без вступившего в силу решения, исполнительный лист без постановления об окончании производства или непроданный залог в обращении взыскания; иначе «не ведётся». Над кредитами разрезы, по умолчанию департамент → заёмщик; строка заёмщика есть всегда, даже при одном кредите. Первая строка — ИТОГО; строка разреза несёт его итог и стоит над своими строками. Порядок: департаменты — по оргструктуре; заёмщики — по алфавиту наименования без организационной формы; кредиты заёмщика — по дате договора. Суммы — в тыс. сом. Кредит в иностранной валюте: списано — по курсу на день каждого списания, поступило — в сомах, как поступили, не возвращено — остаток списанного требования в валюте договора по курсу на дату отчёта, поэтому в сомах разность «списано − поступило» с ним расходится на курсовую разницу. Под валютным кредитом курсивом строка «в тыс. &lt;валюта&gt; (курс …)» — те же суммы в валюте договора, где разность сходится; в итоги она не входит. Печать — A4 альбомная.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1">
+      <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B46" s="32" t="inlineStr">
+        <is>
+          <t>по умолчанию: Департамент → Заёмщик → кредит; можно выбрать: Департамент, Отдел, Куратор, Взыскание, Область, Район, Отрасль, Кредитная программа, Вид кредита, Кредитная линия, Валюта, Год списания, Заёмщик</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="31" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>Списание</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>документ-основание: заключение Постоянно-действующей комиссии, номер и дата (Порядок №41 п. 62–63)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>Всего</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>Списание</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>сумма списанного долга</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>Основная сумма</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>Списание</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>списано основной суммы</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>Проценты</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>Списание</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>списано процентов</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>Штрафы</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>Списание</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>списано штрафов</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>Списание</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>свободная отметка</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Правила проверки</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>Сумма списания по кредиту = сумме списания в карточке кредита (вкладка «Списание»).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>«Всего» = основная сумма + проценты + штрафы в каждой строке.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>КЗ-08 за сентябрь 2026 показан со списанием всего долга; после списания остаток кредита 0,00.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>Подытог и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>5.</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>Списание не входит в «Погашения за период» (ФО-04).</t>
+      <c r="B47" s="32" t="inlineStr">
+        <is>
+          <t>Порядок №41 пп. 62, 65</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="31" t="inlineStr">
+        <is>
+          <t>Образец-основа</t>
+        </is>
+      </c>
+      <c r="B48" s="32" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="31" t="inlineStr">
+        <is>
+          <t>Колонки</t>
+        </is>
+      </c>
+      <c r="B49" s="32" t="inlineStr">
+        <is>
+          <t>Наименование; Дата списания; Взыскание; Заёмщиков; Кредитов; Всего списано; в том числе: по основной сумме; в том числе: по процентам; в том числе: по штрафам; Поступило после списания; Не возвращено</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="31" t="inlineStr">
+        <is>
+          <t>Проверка 1</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="inlineStr">
+        <is>
+          <t>На 01.10.2026: 1 заёмщик, 1 кредит — КЗ-08 № 20-3/052, списан 17.09.2026: списано 900,500 (основная сумма 750,000 + проценты 112,500 + штрафы 38,000), поступило после списания 0,000, не возвращено 900,500; взыскание — «не ведётся»: иска, исполнительного листа и залога в обращении взыскания по кредиту нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
+        <is>
+          <t>Проверка 2</t>
+        </is>
+      </c>
+      <c r="B51" s="32" t="inlineStr">
+        <is>
+          <t>«Всего списано» по кредиту = основному отчёту ФО-11 за период с первого списания по дату отчёта; у кредита в сомах не возвращено = всего списано − поступило после списания; строка разреза = сумма строк ниже.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
+        <is>
+          <t>Проверка 3</t>
+        </is>
+      </c>
+      <c r="B52" s="32" t="inlineStr">
+        <is>
+          <t>Остаток списанного кредита в ФО-02 — 0,00, и в просрочку (ФО-01) он не попадает; поступление после списания в ФО-04 — обычный платёж.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="33">
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B49:C49"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B50:C50"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/docs/perechen-otchetov/obrazcy/ФО-11.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-11.xlsx
@@ -1699,7 +1699,7 @@
       </c>
       <c r="B14" s="32" t="inlineStr">
         <is>
-          <t>Строка детали — списание: запись о списании задолженности по решению; в «Наименовании» — документ-основание «&lt;вид документа&gt; № … от …», в колонках — дата списания, вид списания и суммы по статьям. В отчёт попадают записи о списании с датой списания в периоде. Не списание и в отчёт не входят: признание задолженности безнадёжной без решения о списании, закрытие копеечного остатка при погашении, перевод долга (ФО-12), принятие имущества в счёт погашения (ФО-04). Суммы — по трём статьям, как в ФО-02 и ФО-04: основная сумма; проценты — вместе с накопленными и платой за неосвоенный остаток; штрафы — пеня по основной сумме и по процентам вместе с накопленной. Списанные сборы и расходы по взысканию в отчёт не входят. Показывается снятое с кредита — числившееся на день списания: если в документе названа бо́льшая сумма, в отчёте её нет. «Всего списано» = основная сумма + проценты + штрафы. Вид списания — «весь долг», если после списания долг по кредиту (основная сумма, проценты, штрафы) — 0,00 и кредит закрыт, иначе «часть долга». Над списаниями разрезы, по умолчанию департамент → заёмщик → кредит; строка кредита «№ … от …, KGS» есть всегда, даже при одном списании; при разрезе по области у городов республиканского значения — обе строки, области и района. Реквизиты разрезов (департамент, отдел, куратор) — на дату списания. Первая строка — ИТОГО; строка разреза несёт его итог и стоит над своими строками. Порядок: департаменты и отделы — по оргструктуре; заёмщики — по алфавиту наименования без организационной формы; кредиты заёмщика — по дате договора; списания кредита — по дате списания. Суммы — в тыс. сом. Кредит в иностранной валюте: суммы в сомах по курсу на день списания, под строкой списания курсивом строка «в тыс. &lt;валюта&gt; (курс …)» с теми же суммами в валюте договора; в итоги она не входит. Печать — A4 альбомная.</t>
+          <t>Строка детали — списание: запись о списании задолженности по решению; в «Наименовании» — документ-основание «&lt;вид документа&gt; № … от …», в колонках — дата списания, вид списания и суммы по статьям. В отчёт попадают записи о списании с датой списания в периоде. Не списание и в отчёт не входят: признание задолженности безнадёжной без решения о списании, закрытие копеечного остатка при погашении, перевод долга (ФО-58), принятие имущества в счёт погашения (ФО-04). Суммы — по трём статьям, как в ФО-02 и ФО-04: основная сумма; проценты — вместе с накопленными и платой за неосвоенный остаток; штрафы — пеня по основной сумме и по процентам вместе с накопленной. Списанные сборы и расходы по взысканию в отчёт не входят. Показывается снятое с кредита — числившееся на день списания: если в документе названа бо́льшая сумма, в отчёте её нет. «Всего списано» = основная сумма + проценты + штрафы. Вид списания — «весь долг», если после списания долг по кредиту (основная сумма, проценты, штрафы) — 0,00 и кредит закрыт, иначе «часть долга». Над списаниями разрезы, по умолчанию департамент → заёмщик → кредит; строка кредита «№ … от …, KGS» есть всегда, даже при одном списании; при разрезе по области у городов республиканского значения — обе строки, области и района. Реквизиты разрезов (департамент, отдел, куратор) — на дату списания. Первая строка — ИТОГО; строка разреза несёт его итог и стоит над своими строками. Порядок: департаменты и отделы — по оргструктуре; заёмщики — по алфавиту наименования без организационной формы; кредиты заёмщика — по дате договора; списания кредита — по дате списания. Суммы — в тыс. сом. Кредит в иностранной валюте: суммы в сомах по курсу на день списания, под строкой списания курсивом строка «в тыс. &lt;валюта&gt; (курс …)» с теми же суммами в валюте договора; в итоги она не входит. Печать — A4 альбомная.</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B38" s="32" t="inlineStr">
         <is>
-          <t>Не попадают: КЗ-15 (погашен 18.09.2026 — ФО-95), КЗ-07 (перевод долга 09.09.2026 — ФО-12), КЗ-16 (погашен имуществом 20.03.2026 — ФО-04), кредиты в группе «4. Безнадёжные долги» без решения о списании.</t>
+          <t>Не попадают: КЗ-15 (погашен 18.09.2026 — ФО-95), КЗ-07 (перевод долга 09.09.2026 — ФО-58), КЗ-16 (погашен имуществом 20.03.2026 — ФО-04), кредиты в группе «4. Безнадёжные долги» без решения о списании.</t>
         </is>
       </c>
     </row>
